--- a/data/raw/sales/Week 29/Audio_Array/other_channels.xlsx
+++ b/data/raw/sales/Week 29/Audio_Array/other_channels.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\sales\Week 29\Audio_Array\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\Nitesh Gdrive\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\sales\Week 29\Audio_Array\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03980EC0-53F7-4E0A-A99D-333194387F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -659,28 +659,33 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
